--- a/travel/2026-11_JANES/出張日程表_11月7日_北ヨーロッパ学会.xlsx
+++ b/travel/2026-11_JANES/出張日程表_11月7日_北ヨーロッパ学会.xlsx
@@ -1005,7 +1005,7 @@
       <c r="C3" s="64" t="n"/>
       <c r="D3" s="65" t="inlineStr">
         <is>
-          <t>東海大学 品川キャンパス（東京都港区高輪2-3-23）</t>
+          <t>東海大学 品川キャンパス 4号館（東京都港区高輪2-3-23）</t>
         </is>
       </c>
       <c r="E3" s="83" t="n"/>
@@ -1156,7 +1156,7 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="39" t="inlineStr">
         <is>
-          <t>山陽・東海道新幹線（のぞみ）</t>
+          <t>のぞみ（始発付近の便）</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       <c r="C12" s="62" t="n"/>
       <c r="D12" s="62" t="inlineStr">
         <is>
-          <t>9時半頃</t>
+          <t>9時40分頃</t>
         </is>
       </c>
       <c r="E12" s="56" t="inlineStr">
@@ -1187,7 +1187,7 @@
       <c r="C13" s="62" t="n"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10時頃</t>
+          <t>10時</t>
         </is>
       </c>
       <c r="E13" s="56" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F13" s="59" t="inlineStr">
         <is>
-          <t>東海大学 品川キャンパス</t>
+          <t>東海大学 品川キャンパス 4号館</t>
         </is>
       </c>
       <c r="G13" s="11" t="n">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="H13" s="97" t="inlineStr">
         <is>
-          <t>北ヨーロッパ学会 2026年度研究大会・総会に参加（共通論題「北欧学の新展開」）</t>
+          <t>北ヨーロッパ学会 2026年度研究大会。セッション②自由論題「環境」（10時30分～12時10分、ROOM2）にて研究報告「マンカラ原則とフィンランド自治体エネルギー事業―北欧比較からみる自治体財政基盤の形成」</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1222,51 +1222,55 @@
     <row r="14" ht="19.9" customFormat="1" customHeight="1" s="3">
       <c r="A14" s="91" t="n"/>
       <c r="C14" s="62" t="n"/>
-      <c r="D14" s="62" t="inlineStr">
-        <is>
-          <t>19時半頃</t>
-        </is>
-      </c>
-      <c r="E14" s="56" t="inlineStr">
-        <is>
-          <t>品川駅</t>
-        </is>
-      </c>
+      <c r="D14" s="62" t="n"/>
+      <c r="E14" s="56" t="n"/>
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="11" t="n"/>
-      <c r="H14" s="97" t="n"/>
+      <c r="H14" s="97" t="inlineStr">
+        <is>
+          <t>総会（13時10分～13時40分）、共通論題「北欧学の新展開」（13時50分～15時50分）、自由論題セッション（16時～17時40分）に参加</t>
+        </is>
+      </c>
       <c r="I14" s="11" t="n"/>
-      <c r="J14" s="96" t="inlineStr">
-        <is>
-          <t>のぞみ</t>
-        </is>
-      </c>
+      <c r="J14" s="96" t="n"/>
     </row>
     <row r="15" ht="19.9" customFormat="1" customHeight="1" s="3">
       <c r="A15" s="91" t="n"/>
       <c r="C15" s="62" t="n"/>
       <c r="D15" s="58" t="inlineStr">
         <is>
-          <t>23時頃</t>
+          <t>18時頃</t>
         </is>
       </c>
       <c r="E15" s="57" t="inlineStr">
         <is>
-          <t>福山駅（自宅）</t>
+          <t>品川駅</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="98" t="n"/>
       <c r="I15" s="28" t="n"/>
-      <c r="J15" s="39" t="n"/>
+      <c r="J15" s="39" t="inlineStr">
+        <is>
+          <t>のぞみ</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19.9" customFormat="1" customHeight="1" s="3">
-      <c r="A16" s="61" t="n"/>
+      <c r="A16" s="91" t="n"/>
       <c r="C16" s="62" t="n"/>
-      <c r="D16" s="58" t="n"/>
-      <c r="E16" s="57" t="n"/>
+      <c r="D16" s="58" t="inlineStr">
+        <is>
+          <t>21時半頃</t>
+        </is>
+      </c>
+      <c r="E16" s="57" t="inlineStr">
+        <is>
+          <t>福山駅（自宅）</t>
+        </is>
+      </c>
       <c r="G16" s="11" t="n"/>
-      <c r="H16" s="43" t="n"/>
+      <c r="H16" s="97" t="n"/>
       <c r="I16" s="28" t="n"/>
       <c r="J16" s="39" t="n"/>
     </row>
